--- a/GPIpuget/project/Efficiency.xlsx
+++ b/GPIpuget/project/Efficiency.xlsx
@@ -58,10 +58,7 @@
     <t>Missing Bio Symbol Files</t>
   </si>
   <si>
-    <t>PEBBLEtiehi.bio</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.v</t>
+    <t>No missing bio or symbol files...</t>
   </si>
   <si>
     <t>Missing Nets</t>
@@ -212,6 +209,15 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `a1['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `a1['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
+4 error(s) during elaboration.
 </t>
   </si>
   <si>
@@ -601,6 +607,26 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -614,34 +640,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -656,15 +662,35 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -676,35 +702,35 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -716,15 +742,15 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -736,17 +762,17 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -756,141 +782,126 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1016,7 +1027,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1034,24 +1045,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1061,37 +1067,37 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1101,22 +1107,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1126,22 +1132,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1151,22 +1157,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1176,24 +1182,24 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>1</v>

--- a/GPIpuget/project/Efficiency.xlsx
+++ b/GPIpuget/project/Efficiency.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="65">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -58,7 +58,10 @@
     <t>Missing Bio Symbol Files</t>
   </si>
   <si>
-    <t>No missing bio or symbol files...</t>
+    <t>PEBBLEtiehi.bio</t>
+  </si>
+  <si>
+    <t>PEBBLEtiehi.v</t>
   </si>
   <si>
     <t>Missing Nets</t>
@@ -213,10 +216,10 @@
   </si>
   <si>
     <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `a1['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `a1['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: can not select part of scalar: a1
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: can not select part of scalar: a1
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Failed to elaborate port expression.
 4 error(s) during elaboration.
 </t>
   </si>
@@ -607,7 +610,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -627,7 +630,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -647,7 +650,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -662,7 +665,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -677,7 +680,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -697,14 +700,14 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
     </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -717,14 +720,14 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -737,12 +740,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -757,7 +760,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -777,132 +780,132 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -917,7 +920,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -962,62 +965,62 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>61</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1027,7 +1030,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1045,6 +1048,11 @@
         <v>7</v>
       </c>
     </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1057,7 +1065,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1067,22 +1075,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1105,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1107,7 +1115,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1122,7 +1130,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1132,7 +1140,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1147,7 +1155,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1157,7 +1165,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1172,7 +1180,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1182,7 +1190,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1197,7 +1205,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Efficiency.xlsx
+++ b/GPIpuget/project/Efficiency.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="63">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -43,10 +43,10 @@
     <t>0</t>
   </si>
   <si>
-    <t>Overview</t>
-  </si>
-  <si>
-    <t>Your schematic contains no net zero.</t>
+    <t>XGPI,XMAIN</t>
+  </si>
+  <si>
+    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
   </si>
   <si>
     <t>Validate no "text" in Datamaps</t>
@@ -68,9 +68,6 @@
   </si>
   <si>
     <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -212,15 +209,6 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: can not select part of scalar: a1
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: can not select part of scalar: a1
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Failed to elaborate port expression.
-4 error(s) during elaboration.
 </t>
   </si>
   <si>
@@ -610,6 +598,26 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -623,34 +631,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -665,15 +653,35 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -685,35 +693,35 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -725,15 +733,15 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -745,17 +753,17 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -765,162 +773,137 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>58</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -965,62 +948,62 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>61</v>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1080,32 +1063,32 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1115,22 +1098,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1140,22 +1123,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1165,22 +1148,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1190,24 +1173,24 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>1</v>

--- a/GPIpuget/project/Efficiency.xlsx
+++ b/GPIpuget/project/Efficiency.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="64">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -209,6 +209,15 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Failed to elaborate port expression.
+4 error(s) during elaboration.
 </t>
   </si>
   <si>
@@ -763,7 +772,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -891,6 +900,11 @@
         <v>56</v>
       </c>
     </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -903,7 +917,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -948,62 +962,62 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>60</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/GPIpuget/project/Efficiency.xlsx
+++ b/GPIpuget/project/Efficiency.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="63">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -209,15 +209,6 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Failed to elaborate port expression.
-4 error(s) during elaboration.
 </t>
   </si>
   <si>
@@ -772,7 +763,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -900,24 +891,19 @@
         <v>56</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>57</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -962,27 +948,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -992,32 +998,12 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/GPIpuget/project/Efficiency.xlsx
+++ b/GPIpuget/project/Efficiency.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="63">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -43,31 +43,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>Your schematic contains no net zero.</t>
+  </si>
+  <si>
+    <t>Validate no "text" in Datamaps</t>
+  </si>
+  <si>
+    <t>No errors</t>
+  </si>
+  <si>
+    <t>Missing Bio Symbol Files</t>
+  </si>
+  <si>
+    <t>No missing bio or symbol files...</t>
+  </si>
+  <si>
+    <t>Missing Nets</t>
+  </si>
+  <si>
+    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
+  </si>
+  <si>
     <t>XGPI,XMAIN</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
-  </si>
-  <si>
-    <t>Validate no "text" in Datamaps</t>
-  </si>
-  <si>
-    <t>No errors</t>
-  </si>
-  <si>
-    <t>Missing Bio Symbol Files</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.bio</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.v</t>
-  </si>
-  <si>
-    <t>Missing Nets</t>
-  </si>
-  <si>
-    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -1013,7 +1013,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1031,24 +1031,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1058,12 +1053,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">

--- a/GPIpuget/project/Efficiency.xlsx
+++ b/GPIpuget/project/Efficiency.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="64">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -209,6 +209,14 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:362: warning: Port 1 (q) of PEBBLEtielo expects 1 bits, got 7.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:362:        : Padding 6 high bits of the expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:369: warning: Port 1 (q) of PEBBLEtielo expects 1 bits, got 7.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:369:        : Padding 6 high bits of the expression.
 </t>
   </si>
   <si>
@@ -763,7 +771,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -891,6 +899,11 @@
         <v>56</v>
       </c>
     </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -903,7 +916,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -948,62 +961,62 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>60</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/GPIpuget/project/Efficiency.xlsx
+++ b/GPIpuget/project/Efficiency.xlsx
@@ -213,10 +213,11 @@
   </si>
   <si>
     <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:362: warning: Port 1 (q) of PEBBLEtielo expects 1 bits, got 7.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:362:        : Padding 6 high bits of the expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:369: warning: Port 1 (q) of PEBBLEtielo expects 1 bits, got 7.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:369:        : Padding 6 high bits of the expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
+4 error(s) during elaboration.
 </t>
   </si>
   <si>

--- a/GPIpuget/project/Efficiency.xlsx
+++ b/GPIpuget/project/Efficiency.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="63">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -209,15 +209,6 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
-4 error(s) during elaboration.
 </t>
   </si>
   <si>
@@ -772,7 +763,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -900,24 +891,19 @@
         <v>56</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>57</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -962,27 +948,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -992,32 +998,12 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/GPIpuget/project/Efficiency.xlsx
+++ b/GPIpuget/project/Efficiency.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="66">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -68,6 +68,12 @@
   </si>
   <si>
     <t>XGPI,XMAIN</t>
+  </si>
+  <si>
+    <t>XU6,trim_vbuffer_negative</t>
+  </si>
+  <si>
+    <t>XU6,trim_vbuffer_positive</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -209,6 +215,15 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `TBD_XGPI_XMAIN_XU6_trim_vbuffer_negative['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `TBD_XGPI_XMAIN_XU6_trim_vbuffer_positive['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
+4 error(s) during elaboration.
 </t>
   </si>
   <si>
@@ -598,7 +613,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -618,7 +633,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -638,7 +653,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -653,7 +668,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -668,7 +683,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -688,12 +703,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -708,12 +723,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -728,14 +743,14 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -748,7 +763,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -763,132 +778,137 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>33</v>
+  <dimension ref="A1:A49"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>56</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -903,7 +923,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -948,17 +968,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -973,7 +993,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -993,17 +1013,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1038,7 +1058,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1071,37 +1091,22 @@
         <v>12</v>
       </c>
     </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1126,7 +1131,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1151,7 +1156,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1176,6 +1181,31 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
@@ -1183,7 +1213,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Efficiency.xlsx
+++ b/GPIpuget/project/Efficiency.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="62">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -43,10 +43,10 @@
     <t>0</t>
   </si>
   <si>
-    <t>Overview</t>
-  </si>
-  <si>
-    <t>Your schematic contains no net zero.</t>
+    <t>XGPI,XMAIN</t>
+  </si>
+  <si>
+    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
   </si>
   <si>
     <t>Validate no "text" in Datamaps</t>
@@ -65,15 +65,6 @@
   </si>
   <si>
     <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN</t>
-  </si>
-  <si>
-    <t>XU6,trim_vbuffer_negative</t>
-  </si>
-  <si>
-    <t>XU6,trim_vbuffer_positive</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -215,15 +206,6 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `TBD_XGPI_XMAIN_XU6_trim_vbuffer_negative['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `TBD_XGPI_XMAIN_XU6_trim_vbuffer_positive['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
-4 error(s) during elaboration.
 </t>
   </si>
   <si>
@@ -613,7 +595,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -633,7 +615,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -653,7 +635,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -668,6 +650,46 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
     </row>
@@ -676,7 +698,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -688,15 +710,15 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -708,17 +730,37 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -728,187 +770,122 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -923,7 +900,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -968,17 +945,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -993,7 +970,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1013,17 +990,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1058,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1078,42 +1055,32 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1123,7 +1090,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1138,7 +1105,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1148,7 +1115,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1163,7 +1130,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1173,7 +1140,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1188,7 +1155,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1198,7 +1165,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1213,7 +1180,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Efficiency.xlsx
+++ b/GPIpuget/project/Efficiency.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="63">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -43,28 +43,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>Your schematic contains no net zero.</t>
+  </si>
+  <si>
+    <t>Validate no "text" in Datamaps</t>
+  </si>
+  <si>
+    <t>No errors</t>
+  </si>
+  <si>
+    <t>Missing Bio Symbol Files</t>
+  </si>
+  <si>
+    <t>No missing bio or symbol files...</t>
+  </si>
+  <si>
+    <t>Missing Nets</t>
+  </si>
+  <si>
+    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
+  </si>
+  <si>
     <t>XGPI,XMAIN</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
-  </si>
-  <si>
-    <t>Validate no "text" in Datamaps</t>
-  </si>
-  <si>
-    <t>No errors</t>
-  </si>
-  <si>
-    <t>Missing Bio Symbol Files</t>
-  </si>
-  <si>
-    <t>No missing bio or symbol files...</t>
-  </si>
-  <si>
-    <t>Missing Nets</t>
-  </si>
-  <si>
-    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -595,7 +598,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -615,7 +618,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -635,7 +638,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -650,7 +653,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -665,7 +668,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -685,14 +688,14 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
     </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -705,14 +708,14 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -725,12 +728,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -745,7 +748,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -765,127 +768,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -900,7 +903,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -945,62 +948,62 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
         <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>59</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1055,17 +1058,17 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1080,7 +1083,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1090,7 +1093,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1105,7 +1108,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1115,7 +1118,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1130,7 +1133,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1140,7 +1143,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1155,7 +1158,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1165,7 +1168,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1180,7 +1183,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">
